--- a/DATA TABLE.xlsx
+++ b/DATA TABLE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91904\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phara\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5692FFB-F5CD-47FF-BE91-757E54E9C2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DAE0A0-31C2-4FF8-9066-E33D06398CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{515635FD-2638-4227-BDAD-1E50C1A9F0D1}"/>
   </bookViews>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>strain%</t>
-  </si>
-  <si>
-    <t>eps (%/h)</t>
   </si>
   <si>
     <t>tra</t>
@@ -113,6 +110,9 @@
   <si>
     <t>Cobalt Based 25Cr-10Ni-7.5W-B Superalloy Castings</t>
   </si>
+  <si>
+    <t>eps</t>
+  </si>
 </sst>
 </file>
 
@@ -173,9 +173,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -213,7 +213,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -319,7 +319,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -461,7 +461,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -483,19 +483,19 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -509,19 +509,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>450</v>
+        <v>723.15</v>
       </c>
       <c r="D2">
         <v>419.3</v>
       </c>
       <c r="E2">
-        <v>4.1100000000000003</v>
+        <v>4.110000000000001E-5</v>
       </c>
       <c r="F2">
         <v>431</v>
@@ -535,19 +535,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>450</v>
+        <v>723.15</v>
       </c>
       <c r="D3">
         <v>1576.1</v>
       </c>
       <c r="E3">
-        <v>1.36</v>
+        <v>1.3600000000000002E-5</v>
       </c>
       <c r="F3">
         <v>392</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>450</v>
+        <v>723.15</v>
       </c>
       <c r="D4">
         <v>3130</v>
       </c>
       <c r="E4">
-        <v>0.68600000000000005</v>
+        <v>6.8600000000000012E-6</v>
       </c>
       <c r="F4">
         <v>373</v>
@@ -587,19 +587,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>450</v>
+        <v>723.15</v>
       </c>
       <c r="D5">
         <v>6852.9</v>
       </c>
       <c r="E5">
-        <v>0.52500000000000002</v>
+        <v>5.2500000000000006E-6</v>
       </c>
       <c r="F5">
         <v>353</v>
@@ -613,19 +613,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>450</v>
+        <v>723.15</v>
       </c>
       <c r="D6">
         <v>18347.2</v>
       </c>
       <c r="E6">
-        <v>0.22500000000000001</v>
+        <v>2.2500000000000001E-6</v>
       </c>
       <c r="F6">
         <v>333</v>
@@ -639,19 +639,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>450</v>
+        <v>723.15</v>
       </c>
       <c r="D7">
         <v>112506</v>
       </c>
       <c r="E7">
-        <v>3.1099999999999999E-2</v>
+        <v>3.1100000000000002E-7</v>
       </c>
       <c r="F7">
         <v>294</v>
@@ -665,19 +665,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>475</v>
+        <v>748.15</v>
       </c>
       <c r="D8">
         <v>245.2</v>
       </c>
       <c r="E8">
-        <v>11.7</v>
+        <v>1.17E-4</v>
       </c>
       <c r="F8">
         <v>392</v>
@@ -691,19 +691,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>475</v>
+        <v>748.15</v>
       </c>
       <c r="D9">
         <v>998.3</v>
       </c>
       <c r="E9">
-        <v>3.34</v>
+        <v>3.3399999999999999E-5</v>
       </c>
       <c r="F9">
         <v>353</v>
@@ -717,19 +717,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>475</v>
+        <v>748.15</v>
       </c>
       <c r="D10">
         <v>2261.4</v>
       </c>
       <c r="E10">
-        <v>1.8</v>
+        <v>1.8E-5</v>
       </c>
       <c r="F10">
         <v>333</v>
@@ -743,19 +743,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>475</v>
+        <v>748.15</v>
       </c>
       <c r="D11">
         <v>8841.7000000000007</v>
       </c>
       <c r="E11">
-        <v>0.50600000000000001</v>
+        <v>5.0600000000000007E-6</v>
       </c>
       <c r="F11">
         <v>294</v>
@@ -769,19 +769,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D12">
         <v>438.1</v>
       </c>
       <c r="E12">
-        <v>10.4</v>
+        <v>1.0400000000000001E-4</v>
       </c>
       <c r="F12">
         <v>333</v>
@@ -795,19 +795,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D13">
         <v>2426.4</v>
       </c>
       <c r="E13">
-        <v>1.84</v>
+        <v>1.8400000000000003E-5</v>
       </c>
       <c r="F13">
         <v>294</v>
@@ -821,19 +821,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D14">
         <v>7682.1</v>
       </c>
       <c r="E14">
-        <v>0.432</v>
+        <v>4.3200000000000001E-6</v>
       </c>
       <c r="F14">
         <v>265</v>
@@ -847,19 +847,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D15">
         <v>14864.4</v>
       </c>
       <c r="E15">
-        <v>0.128</v>
+        <v>1.28E-6</v>
       </c>
       <c r="F15">
         <v>235</v>
@@ -873,19 +873,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D16">
         <v>26667.4</v>
       </c>
       <c r="E16">
-        <v>8.1500000000000003E-2</v>
+        <v>8.1500000000000014E-7</v>
       </c>
       <c r="F16">
         <v>216</v>
@@ -899,19 +899,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17">
-        <v>525</v>
+        <v>798.15</v>
       </c>
       <c r="D17">
         <v>406.6</v>
       </c>
       <c r="E17">
-        <v>10.8</v>
+        <v>1.0800000000000001E-4</v>
       </c>
       <c r="F17">
         <v>294</v>
@@ -925,19 +925,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>525</v>
+        <v>798.15</v>
       </c>
       <c r="D18">
         <v>1208.5</v>
       </c>
       <c r="E18">
-        <v>3.15</v>
+        <v>3.15E-5</v>
       </c>
       <c r="F18">
         <v>265</v>
@@ -951,19 +951,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19">
-        <v>525</v>
+        <v>798.15</v>
       </c>
       <c r="D19">
         <v>2881.5</v>
       </c>
       <c r="E19">
-        <v>0.80600000000000005</v>
+        <v>8.0600000000000008E-6</v>
       </c>
       <c r="F19">
         <v>235</v>
@@ -977,19 +977,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20">
-        <v>525</v>
+        <v>798.15</v>
       </c>
       <c r="D20">
         <v>7219.3</v>
       </c>
       <c r="E20">
-        <v>0.187</v>
+        <v>1.8700000000000001E-6</v>
       </c>
       <c r="F20">
         <v>196</v>
@@ -1003,19 +1003,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>525</v>
+        <v>798.15</v>
       </c>
       <c r="D21">
         <v>15187.9</v>
       </c>
       <c r="E21">
-        <v>8.2699999999999996E-2</v>
+        <v>8.2699999999999998E-7</v>
       </c>
       <c r="F21">
         <v>177</v>
@@ -1029,19 +1029,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D22">
         <v>679.2</v>
       </c>
       <c r="E22">
-        <v>4.3</v>
+        <v>4.3000000000000002E-5</v>
       </c>
       <c r="F22">
         <v>235</v>
@@ -1055,19 +1055,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D23">
         <v>956.5</v>
       </c>
       <c r="E23">
-        <v>2.09</v>
+        <v>2.09E-5</v>
       </c>
       <c r="F23">
         <v>216</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D24">
         <v>1518.7</v>
       </c>
       <c r="E24">
-        <v>0.89600000000000002</v>
+        <v>8.9600000000000006E-6</v>
       </c>
       <c r="F24">
         <v>196</v>
@@ -1107,19 +1107,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D25">
         <v>2482.8000000000002</v>
       </c>
       <c r="E25">
-        <v>0.503</v>
+        <v>5.0300000000000001E-6</v>
       </c>
       <c r="F25">
         <v>177</v>
@@ -1133,19 +1133,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D26">
         <v>4918.8999999999996</v>
       </c>
       <c r="E26">
-        <v>0.23599999999999999</v>
+        <v>2.3600000000000003E-6</v>
       </c>
       <c r="F26">
         <v>157</v>
@@ -1159,19 +1159,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D27">
         <v>8203</v>
       </c>
       <c r="E27">
-        <v>0.161</v>
+        <v>1.6100000000000003E-6</v>
       </c>
       <c r="F27">
         <v>137</v>
@@ -1185,19 +1185,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D28">
         <v>16752.2</v>
       </c>
       <c r="E28">
-        <v>8.0799999999999997E-2</v>
+        <v>8.0800000000000004E-7</v>
       </c>
       <c r="F28">
         <v>118</v>
@@ -1211,19 +1211,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D29">
         <v>15.7</v>
       </c>
       <c r="E29">
-        <v>290</v>
+        <v>2.9000000000000002E-3</v>
       </c>
       <c r="F29">
         <v>300</v>
@@ -1237,19 +1237,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D30">
         <v>78.400000000000006</v>
       </c>
       <c r="E30">
-        <v>48</v>
+        <v>4.8000000000000007E-4</v>
       </c>
       <c r="F30">
         <v>280</v>
@@ -1263,19 +1263,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D31">
         <v>170.1</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>1.9000000000000001E-4</v>
       </c>
       <c r="F31">
         <v>260</v>
@@ -1289,19 +1289,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D32">
         <v>404.4</v>
       </c>
       <c r="E32">
-        <v>7.8</v>
+        <v>7.7999999999999999E-5</v>
       </c>
       <c r="F32">
         <v>250</v>
@@ -1315,19 +1315,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D33">
         <v>1977.8</v>
       </c>
       <c r="E33">
-        <v>1.8</v>
+        <v>1.8E-5</v>
       </c>
       <c r="F33">
         <v>230</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D34">
         <v>7689.8</v>
       </c>
       <c r="E34">
-        <v>0.45</v>
+        <v>4.5000000000000001E-6</v>
       </c>
       <c r="F34">
         <v>220</v>
@@ -1367,19 +1367,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D35">
         <v>48740</v>
       </c>
       <c r="E35">
-        <v>5.7000000000000002E-2</v>
+        <v>5.7000000000000005E-7</v>
       </c>
       <c r="F35">
         <v>190</v>
@@ -1393,19 +1393,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D36">
         <v>109806</v>
       </c>
       <c r="E36">
-        <v>1.9E-2</v>
+        <v>1.9000000000000001E-7</v>
       </c>
       <c r="F36">
         <v>180</v>
@@ -1419,19 +1419,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D37">
         <v>137812</v>
       </c>
       <c r="E37">
-        <v>6.4999999999999997E-3</v>
+        <v>6.5E-8</v>
       </c>
       <c r="F37">
         <v>170</v>
@@ -1445,19 +1445,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D38">
         <v>1568.8</v>
       </c>
       <c r="E38">
-        <v>2.4</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="F38">
         <v>200</v>
@@ -1471,19 +1471,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D39">
         <v>2505.1999999999998</v>
       </c>
       <c r="E39">
-        <v>1.6</v>
+        <v>1.6000000000000003E-5</v>
       </c>
       <c r="F39">
         <v>190</v>
@@ -1497,19 +1497,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D40">
         <v>7472.1</v>
       </c>
       <c r="E40">
-        <v>0.45</v>
+        <v>4.5000000000000001E-6</v>
       </c>
       <c r="F40">
         <v>180</v>
@@ -1523,19 +1523,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D41">
         <v>22923.3</v>
       </c>
       <c r="E41">
-        <v>9.4E-2</v>
+        <v>9.4000000000000011E-7</v>
       </c>
       <c r="F41">
         <v>170</v>
@@ -1549,19 +1549,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D42">
         <v>30879</v>
       </c>
       <c r="E42">
-        <v>7.6999999999999999E-2</v>
+        <v>7.7000000000000004E-7</v>
       </c>
       <c r="F42">
         <v>160</v>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D43">
         <v>11.6</v>
       </c>
       <c r="E43">
-        <v>440</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="F43">
         <v>230</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D44">
         <v>54</v>
       </c>
       <c r="E44">
-        <v>94</v>
+        <v>9.4000000000000008E-4</v>
       </c>
       <c r="F44">
         <v>210</v>
@@ -1627,19 +1627,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D45">
         <v>247.9</v>
       </c>
       <c r="E45">
-        <v>18</v>
+        <v>1.8000000000000001E-4</v>
       </c>
       <c r="F45">
         <v>190</v>
@@ -1653,19 +1653,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D46">
         <v>396.5</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>1.1E-4</v>
       </c>
       <c r="F46">
         <v>180</v>
@@ -1679,19 +1679,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D47">
         <v>2721.5</v>
       </c>
       <c r="E47">
-        <v>1.3</v>
+        <v>1.3000000000000001E-5</v>
       </c>
       <c r="F47">
         <v>160</v>
@@ -1705,19 +1705,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C48">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D48">
         <v>16679.5</v>
       </c>
       <c r="E48">
-        <v>0.12</v>
+        <v>1.2000000000000002E-6</v>
       </c>
       <c r="F48">
         <v>140</v>
@@ -1731,19 +1731,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D49">
         <v>38066.800000000003</v>
       </c>
       <c r="E49">
-        <v>5.0999999999999997E-2</v>
+        <v>5.0999999999999999E-7</v>
       </c>
       <c r="F49">
         <v>130</v>
@@ -1757,19 +1757,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C50">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D50">
         <v>88568.1</v>
       </c>
       <c r="E50">
-        <v>2.1000000000000001E-2</v>
+        <v>2.1000000000000003E-7</v>
       </c>
       <c r="F50">
         <v>120</v>
@@ -1783,19 +1783,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D51">
         <v>98767.8</v>
       </c>
       <c r="E51">
-        <v>1.4999999999999999E-2</v>
+        <v>1.5000000000000002E-7</v>
       </c>
       <c r="F51">
         <v>110</v>
@@ -1809,19 +1809,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D52">
         <v>118943</v>
       </c>
       <c r="E52">
-        <v>7.7999999999999996E-3</v>
+        <v>7.7999999999999997E-8</v>
       </c>
       <c r="F52">
         <v>100</v>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D53">
         <v>213.4</v>
       </c>
       <c r="E53">
-        <v>23</v>
+        <v>2.3000000000000001E-4</v>
       </c>
       <c r="F53">
         <v>160</v>
@@ -1858,19 +1858,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D54">
         <v>1458.2</v>
       </c>
       <c r="E54">
-        <v>2.5</v>
+        <v>2.5000000000000001E-5</v>
       </c>
       <c r="F54">
         <v>140</v>
@@ -1884,19 +1884,19 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D55">
         <v>3886.1</v>
       </c>
       <c r="E55">
-        <v>0.69</v>
+        <v>6.9E-6</v>
       </c>
       <c r="F55">
         <v>130</v>
@@ -1910,19 +1910,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C56">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D56">
         <v>17530</v>
       </c>
       <c r="E56">
-        <v>0.12</v>
+        <v>1.2000000000000002E-6</v>
       </c>
       <c r="F56">
         <v>110</v>
@@ -1936,19 +1936,19 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D57">
         <v>33518.5</v>
       </c>
       <c r="E57">
-        <v>6.3E-2</v>
+        <v>6.3E-7</v>
       </c>
       <c r="F57">
         <v>100</v>
@@ -1962,19 +1962,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C58">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D58">
         <v>103346</v>
       </c>
       <c r="E58">
-        <v>0.02</v>
+        <v>2.0000000000000002E-7</v>
       </c>
       <c r="F58">
         <v>80</v>
@@ -1985,19 +1985,19 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D59">
         <v>10.5</v>
       </c>
       <c r="E59">
-        <v>560</v>
+        <v>5.6000000000000008E-3</v>
       </c>
       <c r="F59">
         <v>160</v>
@@ -2011,19 +2011,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D60">
         <v>66</v>
       </c>
       <c r="E60">
-        <v>80</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="F60">
         <v>140</v>
@@ -2037,19 +2037,19 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C61">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D61">
         <v>194</v>
       </c>
       <c r="E61">
-        <v>23</v>
+        <v>2.3000000000000001E-4</v>
       </c>
       <c r="F61">
         <v>130</v>
@@ -2063,19 +2063,19 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C62">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D62">
         <v>1689.1</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F62">
         <v>110</v>
@@ -2089,19 +2089,19 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C63">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D63">
         <v>3738.1</v>
       </c>
       <c r="E63">
-        <v>0.77</v>
+        <v>7.7000000000000008E-6</v>
       </c>
       <c r="F63">
         <v>100</v>
@@ -2115,19 +2115,19 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C64">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D64">
         <v>10001.9</v>
       </c>
       <c r="E64">
-        <v>0.32</v>
+        <v>3.2000000000000003E-6</v>
       </c>
       <c r="F64">
         <v>90</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D65">
         <v>21718.2</v>
       </c>
       <c r="E65">
-        <v>0.13</v>
+        <v>1.3E-6</v>
       </c>
       <c r="F65">
         <v>80</v>
@@ -2167,19 +2167,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C66">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D66">
         <v>50871.199999999997</v>
       </c>
       <c r="E66">
-        <v>0.06</v>
+        <v>6.0000000000000008E-7</v>
       </c>
       <c r="F66">
         <v>70</v>
@@ -2193,19 +2193,19 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D67">
         <v>92845.2</v>
       </c>
       <c r="E67">
-        <v>2.9000000000000001E-2</v>
+        <v>2.9000000000000003E-7</v>
       </c>
       <c r="F67">
         <v>60</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D68">
         <v>116953</v>
       </c>
       <c r="E68">
-        <v>1.4999999999999999E-2</v>
+        <v>1.5000000000000002E-7</v>
       </c>
       <c r="F68">
         <v>50</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C69">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D69">
         <v>93033.1</v>
       </c>
       <c r="E69">
-        <v>6.0000000000000001E-3</v>
+        <v>6.0000000000000008E-8</v>
       </c>
       <c r="F69">
         <v>40</v>
@@ -2268,19 +2268,19 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C70">
-        <v>675</v>
+        <v>948.15</v>
       </c>
       <c r="D70">
         <v>92.1</v>
       </c>
       <c r="E70">
-        <v>55</v>
+        <v>5.5000000000000003E-4</v>
       </c>
       <c r="F70">
         <v>110</v>
@@ -2294,19 +2294,19 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C71">
-        <v>675</v>
+        <v>948.15</v>
       </c>
       <c r="D71">
         <v>982.1</v>
       </c>
       <c r="E71">
-        <v>3.8</v>
+        <v>3.8000000000000002E-5</v>
       </c>
       <c r="F71">
         <v>90</v>
@@ -2320,19 +2320,19 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C72">
-        <v>675</v>
+        <v>948.15</v>
       </c>
       <c r="D72">
         <v>2054</v>
       </c>
       <c r="E72">
-        <v>1.6</v>
+        <v>1.6000000000000003E-5</v>
       </c>
       <c r="F72">
         <v>80</v>
@@ -2346,19 +2346,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C73">
-        <v>675</v>
+        <v>948.15</v>
       </c>
       <c r="D73">
         <v>16855.8</v>
       </c>
       <c r="E73">
-        <v>0.23</v>
+        <v>2.3000000000000004E-6</v>
       </c>
       <c r="F73">
         <v>60</v>
@@ -2372,19 +2372,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C74">
-        <v>675</v>
+        <v>948.15</v>
       </c>
       <c r="D74">
         <v>38054.800000000003</v>
       </c>
       <c r="E74">
-        <v>7.5999999999999998E-2</v>
+        <v>7.6000000000000003E-7</v>
       </c>
       <c r="F74">
         <v>50</v>
@@ -2398,19 +2398,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C75">
-        <v>675</v>
+        <v>948.15</v>
       </c>
       <c r="D75">
         <v>82993.2</v>
       </c>
       <c r="E75">
-        <v>2.8000000000000001E-2</v>
+        <v>2.8000000000000002E-7</v>
       </c>
       <c r="F75">
         <v>40</v>
@@ -2424,19 +2424,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C76">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D76">
         <v>4.3</v>
       </c>
       <c r="E76">
-        <v>1500</v>
+        <v>1.5000000000000001E-2</v>
       </c>
       <c r="F76">
         <v>120</v>
@@ -2450,19 +2450,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D77">
         <v>25.4</v>
       </c>
       <c r="E77">
-        <v>210</v>
+        <v>2.1000000000000003E-3</v>
       </c>
       <c r="F77">
         <v>100</v>
@@ -2476,19 +2476,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D78">
         <v>117.8</v>
       </c>
       <c r="E78">
-        <v>39</v>
+        <v>3.9000000000000005E-4</v>
       </c>
       <c r="F78">
         <v>85</v>
@@ -2502,19 +2502,19 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D79">
         <v>727.2</v>
       </c>
       <c r="E79">
-        <v>6.8</v>
+        <v>6.7999999999999999E-5</v>
       </c>
       <c r="F79">
         <v>70</v>
@@ -2528,19 +2528,19 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C80">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D80">
         <v>1195.7</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F80">
         <v>60</v>
@@ -2554,19 +2554,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D81">
         <v>6778.4</v>
       </c>
       <c r="E81">
-        <v>0.57999999999999996</v>
+        <v>5.8000000000000004E-6</v>
       </c>
       <c r="F81">
         <v>50</v>
@@ -2580,19 +2580,19 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C82">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D82">
         <v>21880.7</v>
       </c>
       <c r="E82">
-        <v>0.17</v>
+        <v>1.7000000000000002E-6</v>
       </c>
       <c r="F82">
         <v>40</v>
@@ -2606,19 +2606,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C83">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D83">
         <v>23551.4</v>
       </c>
       <c r="E83">
-        <v>0.14000000000000001</v>
+        <v>1.4000000000000001E-6</v>
       </c>
       <c r="F83">
         <v>35</v>
@@ -2632,19 +2632,19 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C84">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D84">
         <v>45094.3</v>
       </c>
       <c r="E84">
-        <v>7.5999999999999998E-2</v>
+        <v>7.6000000000000003E-7</v>
       </c>
       <c r="F84">
         <v>30</v>
@@ -2658,17 +2658,20 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C85">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D85">
         <v>100184.9</v>
       </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
       <c r="F85">
         <v>25</v>
       </c>
@@ -2681,19 +2684,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C86">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D86">
         <v>97</v>
       </c>
       <c r="E86">
-        <v>53</v>
+        <v>5.3000000000000009E-4</v>
       </c>
       <c r="F86">
         <v>50</v>
@@ -2707,19 +2710,19 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C87">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D87">
         <v>429.9</v>
       </c>
       <c r="E87">
-        <v>11</v>
+        <v>1.1E-4</v>
       </c>
       <c r="F87">
         <v>40</v>
@@ -2733,19 +2736,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C88">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D88">
         <v>1994</v>
       </c>
       <c r="E88">
-        <v>2.2000000000000002</v>
+        <v>2.2000000000000003E-5</v>
       </c>
       <c r="F88">
         <v>30</v>
@@ -2759,19 +2762,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C89">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D89">
         <v>3621.2</v>
       </c>
       <c r="E89">
-        <v>0.69</v>
+        <v>6.9E-6</v>
       </c>
       <c r="F89">
         <v>25</v>
@@ -2785,19 +2788,19 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C90">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D90">
         <v>5713.3</v>
       </c>
       <c r="E90">
-        <v>0.3</v>
+        <v>3.0000000000000001E-6</v>
       </c>
       <c r="F90">
         <v>20</v>
@@ -2811,19 +2814,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C91">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D91">
         <v>340.3</v>
       </c>
       <c r="E91">
-        <v>10.199999999999999</v>
+        <v>1.02E-4</v>
       </c>
       <c r="F91">
         <v>471</v>
@@ -2837,19 +2840,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C92">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D92">
         <v>15207.2</v>
       </c>
       <c r="E92">
-        <v>0.14000000000000001</v>
+        <v>1.4000000000000001E-6</v>
       </c>
       <c r="F92">
         <v>373</v>
@@ -2863,19 +2866,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C93">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D93">
         <v>29695</v>
       </c>
       <c r="E93">
-        <v>4.1700000000000001E-2</v>
+        <v>4.1700000000000004E-7</v>
       </c>
       <c r="F93">
         <v>333</v>
@@ -2889,19 +2892,19 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C94">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D94">
         <v>44300</v>
       </c>
       <c r="E94">
-        <v>1.89E-2</v>
+        <v>1.8900000000000001E-7</v>
       </c>
       <c r="F94">
         <v>294</v>
@@ -2915,19 +2918,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C95">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D95">
         <v>91840.6</v>
       </c>
       <c r="E95">
-        <v>5.8900000000000003E-3</v>
+        <v>5.8900000000000005E-8</v>
       </c>
       <c r="F95">
         <v>235</v>
@@ -2941,19 +2944,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C96">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D96">
         <v>208.9</v>
       </c>
       <c r="E96">
-        <v>24.2</v>
+        <v>2.42E-4</v>
       </c>
       <c r="F96">
         <v>373</v>
@@ -2967,19 +2970,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C97">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D97">
         <v>1018.1</v>
       </c>
       <c r="E97">
-        <v>3.27</v>
+        <v>3.2700000000000002E-5</v>
       </c>
       <c r="F97">
         <v>333</v>
@@ -2993,19 +2996,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C98">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D98">
         <v>4142</v>
       </c>
       <c r="E98">
-        <v>0.50700000000000001</v>
+        <v>5.0700000000000006E-6</v>
       </c>
       <c r="F98">
         <v>294</v>
@@ -3019,19 +3022,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C99">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D99">
         <v>7258.2</v>
       </c>
       <c r="E99">
-        <v>0.22</v>
+        <v>2.2000000000000001E-6</v>
       </c>
       <c r="F99">
         <v>265</v>
@@ -3045,19 +3048,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C100">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D100">
         <v>12043.4</v>
       </c>
       <c r="E100">
-        <v>0.115</v>
+        <v>1.1500000000000002E-6</v>
       </c>
       <c r="F100">
         <v>235</v>
@@ -3071,19 +3074,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C101">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D101">
         <v>14967.3</v>
       </c>
       <c r="E101">
-        <v>7.7799999999999994E-2</v>
+        <v>7.7800000000000001E-7</v>
       </c>
       <c r="F101">
         <v>216</v>
@@ -3097,19 +3100,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C102">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D102">
         <v>64271.9</v>
       </c>
       <c r="E102">
-        <v>7.7200000000000003E-3</v>
+        <v>7.7200000000000003E-8</v>
       </c>
       <c r="F102">
         <v>118</v>
@@ -3123,19 +3126,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C103">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D103">
         <v>390.1</v>
       </c>
       <c r="E103">
-        <v>6.1</v>
+        <v>6.0999999999999999E-5</v>
       </c>
       <c r="F103">
         <v>235</v>
@@ -3149,19 +3152,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C104">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D104">
         <v>542</v>
       </c>
       <c r="E104">
-        <v>4.17</v>
+        <v>4.1700000000000004E-5</v>
       </c>
       <c r="F104">
         <v>216</v>
@@ -3175,19 +3178,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C105">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D105">
         <v>5160.2</v>
       </c>
       <c r="E105">
-        <v>0.25700000000000001</v>
+        <v>2.5700000000000004E-6</v>
       </c>
       <c r="F105">
         <v>118</v>
@@ -3201,19 +3204,19 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C106">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D106">
         <v>189.1</v>
       </c>
       <c r="E106">
-        <v>14.8</v>
+        <v>1.4800000000000002E-4</v>
       </c>
       <c r="F106">
         <v>118</v>
@@ -3227,19 +3230,19 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C107">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D107">
         <v>380.6</v>
       </c>
       <c r="E107">
-        <v>7.61</v>
+        <v>7.6100000000000007E-5</v>
       </c>
       <c r="F107">
         <v>98</v>
@@ -3253,19 +3256,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C108">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D108">
         <v>1179.0999999999999</v>
       </c>
       <c r="E108">
-        <v>2.87</v>
+        <v>2.8700000000000003E-5</v>
       </c>
       <c r="F108">
         <v>69</v>
@@ -3279,19 +3282,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C109">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D109">
         <v>10679</v>
       </c>
       <c r="E109">
-        <v>0.222</v>
+        <v>2.2200000000000003E-6</v>
       </c>
       <c r="F109">
         <v>412</v>
@@ -3305,19 +3308,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C110">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D110">
         <v>28403.7</v>
       </c>
       <c r="E110">
-        <v>4.7399999999999998E-2</v>
+        <v>4.7400000000000004E-7</v>
       </c>
       <c r="F110">
         <v>373</v>
@@ -3331,19 +3334,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C111">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D111">
         <v>45634.5</v>
       </c>
       <c r="E111">
-        <v>2.0299999999999999E-2</v>
+        <v>2.03E-7</v>
       </c>
       <c r="F111">
         <v>333</v>
@@ -3357,19 +3360,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C112">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D112">
         <v>62733.7</v>
       </c>
       <c r="E112">
-        <v>9.5999999999999992E-3</v>
+        <v>9.5999999999999999E-8</v>
       </c>
       <c r="F112">
         <v>294</v>
@@ -3383,19 +3386,19 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C113">
-        <v>500</v>
+        <v>773.15</v>
       </c>
       <c r="D113">
         <v>79769</v>
       </c>
       <c r="E113">
-        <v>6.6100000000000004E-3</v>
+        <v>6.6100000000000016E-8</v>
       </c>
       <c r="F113">
         <v>265</v>
@@ -3409,19 +3412,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C114">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D114">
         <v>2109.1</v>
       </c>
       <c r="E114">
-        <v>1.26</v>
+        <v>1.2600000000000001E-5</v>
       </c>
       <c r="F114">
         <v>333</v>
@@ -3435,19 +3438,19 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C115">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D115">
         <v>6426.3</v>
       </c>
       <c r="E115">
-        <v>0.29499999999999998</v>
+        <v>2.9500000000000001E-6</v>
       </c>
       <c r="F115">
         <v>294</v>
@@ -3461,19 +3464,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C116">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D116">
         <v>11431.5</v>
       </c>
       <c r="E116">
-        <v>0.13300000000000001</v>
+        <v>1.3300000000000002E-6</v>
       </c>
       <c r="F116">
         <v>265</v>
@@ -3487,19 +3490,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C117">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D117">
         <v>21534.799999999999</v>
       </c>
       <c r="E117">
-        <v>5.7099999999999998E-2</v>
+        <v>5.7100000000000002E-7</v>
       </c>
       <c r="F117">
         <v>235</v>
@@ -3513,19 +3516,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C118">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D118">
         <v>28637</v>
       </c>
       <c r="E118">
-        <v>3.6499999999999998E-2</v>
+        <v>3.65E-7</v>
       </c>
       <c r="F118">
         <v>216</v>
@@ -3539,19 +3542,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C119">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D119">
         <v>983.2</v>
       </c>
       <c r="E119">
-        <v>1.78</v>
+        <v>1.7800000000000002E-5</v>
       </c>
       <c r="F119">
         <v>216</v>
@@ -3565,19 +3568,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C120">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D120">
         <v>514.20000000000005</v>
       </c>
       <c r="E120">
-        <v>5.86</v>
+        <v>5.8600000000000008E-5</v>
       </c>
       <c r="F120">
         <v>98</v>
@@ -3591,19 +3594,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C121">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D121">
         <v>1929.5</v>
       </c>
       <c r="E121">
-        <v>1.73</v>
+        <v>1.73E-5</v>
       </c>
       <c r="F121">
         <v>69</v>
@@ -3617,19 +3620,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C122">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D122">
         <v>7050.9</v>
       </c>
       <c r="E122">
-        <v>0.22</v>
+        <v>2.2000000000000001E-6</v>
       </c>
       <c r="F122">
         <v>235</v>
@@ -3643,19 +3646,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C123">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D123">
         <v>96.6</v>
       </c>
       <c r="E123">
-        <v>169</v>
+        <v>1.6900000000000001E-3</v>
       </c>
       <c r="F123">
         <v>157</v>
@@ -3669,19 +3672,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C124">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D124">
         <v>41583.800000000003</v>
       </c>
       <c r="E124">
-        <v>1.43E-2</v>
+        <v>1.4300000000000002E-7</v>
       </c>
       <c r="F124">
         <v>61</v>
@@ -3695,19 +3698,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B125" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C125">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D125">
         <v>471.9</v>
       </c>
       <c r="E125">
-        <v>50.2</v>
+        <v>5.0200000000000006E-4</v>
       </c>
       <c r="F125">
         <v>61</v>
@@ -3721,19 +3724,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B126" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C126">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D126">
         <v>8449.4</v>
       </c>
       <c r="E126">
-        <v>0.63700000000000001</v>
+        <v>6.3700000000000008E-6</v>
       </c>
       <c r="F126">
         <v>41</v>
@@ -3747,19 +3750,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C127">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D127">
         <v>39104.300000000003</v>
       </c>
       <c r="E127">
-        <v>5.6899999999999997E-3</v>
+        <v>5.69E-8</v>
       </c>
       <c r="F127">
         <v>33</v>
@@ -3773,19 +3776,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B128" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C128">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D128">
         <v>47866.8</v>
       </c>
       <c r="E128">
-        <v>2.1299999999999999E-2</v>
+        <v>2.1300000000000001E-7</v>
       </c>
       <c r="F128">
         <v>29</v>
@@ -3799,19 +3802,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C129">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D129">
         <v>837.2</v>
       </c>
       <c r="E129">
-        <v>2.78</v>
+        <v>2.7800000000000001E-5</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -3825,19 +3828,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C130">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D130">
         <v>1633.1</v>
       </c>
       <c r="E130">
-        <v>0.82299999999999995</v>
+        <v>8.2300000000000008E-6</v>
       </c>
       <c r="F130">
         <v>26</v>
@@ -3851,19 +3854,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C131">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D131">
         <v>28715.599999999999</v>
       </c>
       <c r="E131">
-        <v>0.26600000000000001</v>
+        <v>2.6600000000000004E-6</v>
       </c>
       <c r="F131">
         <v>20</v>
@@ -3877,19 +3880,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C132">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D132">
         <v>62831.1</v>
       </c>
       <c r="E132">
-        <v>9.1399999999999995E-2</v>
+        <v>9.1400000000000006E-7</v>
       </c>
       <c r="F132">
         <v>18</v>
@@ -3903,17 +3906,20 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B133" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C133">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D133">
         <v>26145.9</v>
       </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
       <c r="F133">
         <v>7</v>
       </c>
@@ -3926,19 +3932,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C134">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D134">
         <v>3820.4</v>
       </c>
       <c r="E134">
-        <v>0.215</v>
+        <v>2.1500000000000002E-6</v>
       </c>
       <c r="F134">
         <v>53</v>
@@ -3952,19 +3958,19 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C135">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D135">
         <v>10964.6</v>
       </c>
       <c r="E135">
-        <v>3.7999999999999999E-2</v>
+        <v>3.8000000000000001E-7</v>
       </c>
       <c r="F135">
         <v>41</v>
@@ -3978,19 +3984,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B136" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C136">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D136">
         <v>22587.8</v>
       </c>
       <c r="E136">
-        <v>2.63E-2</v>
+        <v>2.6300000000000001E-7</v>
       </c>
       <c r="F136">
         <v>33</v>
@@ -4004,19 +4010,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C137">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D137">
         <v>41862.1</v>
       </c>
       <c r="E137">
-        <v>1.2500000000000001E-2</v>
+        <v>1.2500000000000002E-7</v>
       </c>
       <c r="F137">
         <v>26</v>
@@ -4030,19 +4036,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B138" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C138">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D138">
         <v>24759.8</v>
       </c>
       <c r="E138">
-        <v>0.21099999999999999</v>
+        <v>2.1100000000000001E-6</v>
       </c>
       <c r="F138">
         <v>14</v>
@@ -4056,19 +4062,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C139">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D139">
         <v>98103.9</v>
       </c>
       <c r="E139">
-        <v>2.9499999999999998E-2</v>
+        <v>2.9500000000000003E-7</v>
       </c>
       <c r="F139">
         <v>10</v>
@@ -4082,19 +4088,19 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C140">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D140">
         <v>40869</v>
       </c>
       <c r="E140">
-        <v>0.17899999999999999</v>
+        <v>1.79E-6</v>
       </c>
       <c r="F140">
         <v>5</v>
@@ -4108,19 +4114,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C141">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D141">
         <v>668.8</v>
       </c>
       <c r="E141">
-        <v>0.31</v>
+        <v>3.1000000000000004E-6</v>
       </c>
       <c r="F141">
         <v>314</v>
@@ -4134,19 +4140,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C142">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D142">
         <v>2861.5</v>
       </c>
       <c r="E142">
-        <v>0.106</v>
+        <v>1.06E-6</v>
       </c>
       <c r="F142">
         <v>284</v>
@@ -4160,19 +4166,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C143">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D143">
         <v>7550.7</v>
       </c>
       <c r="E143">
-        <v>3.8300000000000001E-2</v>
+        <v>3.8300000000000003E-7</v>
       </c>
       <c r="F143">
         <v>265</v>
@@ -4186,19 +4192,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C144">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D144">
         <v>19029.8</v>
       </c>
       <c r="E144">
-        <v>1.06E-2</v>
+        <v>1.0600000000000001E-7</v>
       </c>
       <c r="F144">
         <v>235</v>
@@ -4212,19 +4218,19 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C145">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D145">
         <v>20376</v>
       </c>
       <c r="E145">
-        <v>6.1000000000000004E-3</v>
+        <v>6.1000000000000004E-8</v>
       </c>
       <c r="F145">
         <v>196</v>
@@ -4235,19 +4241,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B146" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C146">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D146">
         <v>6053.8</v>
       </c>
       <c r="E146">
-        <v>3.7699999999999997E-2</v>
+        <v>3.77E-7</v>
       </c>
       <c r="F146">
         <v>216</v>
@@ -4261,19 +4267,19 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C147">
-        <v>575</v>
+        <v>848.15</v>
       </c>
       <c r="D147">
         <v>20400</v>
       </c>
       <c r="E147">
-        <v>1.5299999999999999E-2</v>
+        <v>1.5300000000000001E-7</v>
       </c>
       <c r="F147">
         <v>157</v>
@@ -4284,19 +4290,19 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C148">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D148">
         <v>347.7</v>
       </c>
       <c r="E148">
-        <v>0.877</v>
+        <v>8.7700000000000007E-6</v>
       </c>
       <c r="F148">
         <v>265</v>
@@ -4310,19 +4316,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C149">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D149">
         <v>1530</v>
       </c>
       <c r="E149">
-        <v>0.29599999999999999</v>
+        <v>2.96E-6</v>
       </c>
       <c r="F149">
         <v>216</v>
@@ -4336,19 +4342,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C150">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D150">
         <v>1420.7</v>
       </c>
       <c r="E150">
-        <v>0.23400000000000001</v>
+        <v>2.3400000000000005E-6</v>
       </c>
       <c r="F150">
         <v>216</v>
@@ -4362,19 +4368,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C151">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D151">
         <v>9643.2000000000007</v>
       </c>
       <c r="E151">
-        <v>5.3900000000000003E-2</v>
+        <v>5.3900000000000005E-7</v>
       </c>
       <c r="F151">
         <v>157</v>
@@ -4388,19 +4394,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C152">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D152">
         <v>19574.400000000001</v>
       </c>
       <c r="E152">
-        <v>3.9899999999999998E-2</v>
+        <v>3.9900000000000001E-7</v>
       </c>
       <c r="F152">
         <v>137</v>
@@ -4414,19 +4420,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B153" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C153">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D153">
         <v>37687.5</v>
       </c>
       <c r="E153">
-        <v>2.24E-2</v>
+        <v>2.2400000000000002E-7</v>
       </c>
       <c r="F153">
         <v>118</v>
@@ -4440,19 +4446,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C154">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D154">
         <v>54358.9</v>
       </c>
       <c r="E154">
-        <v>9.8700000000000003E-3</v>
+        <v>9.8700000000000017E-8</v>
       </c>
       <c r="F154">
         <v>108</v>
@@ -4466,19 +4472,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B155" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C155">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D155">
         <v>88531</v>
       </c>
       <c r="E155">
-        <v>9.1299999999999992E-3</v>
+        <v>9.1300000000000004E-8</v>
       </c>
       <c r="F155">
         <v>98</v>
@@ -4492,19 +4498,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B156" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C156">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D156">
         <v>117957.7</v>
       </c>
       <c r="E156">
-        <v>3.98E-3</v>
+        <v>3.9800000000000006E-8</v>
       </c>
       <c r="F156">
         <v>88</v>
@@ -4518,19 +4524,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B157" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C157">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D157">
         <v>3460.9</v>
       </c>
       <c r="E157">
-        <v>7.9500000000000001E-2</v>
+        <v>7.9500000000000012E-7</v>
       </c>
       <c r="F157">
         <v>157</v>
@@ -4544,19 +4550,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B158" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C158">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D158">
         <v>15557.4</v>
       </c>
       <c r="E158">
-        <v>4.2799999999999998E-2</v>
+        <v>4.2800000000000002E-7</v>
       </c>
       <c r="F158">
         <v>118</v>
@@ -4570,19 +4576,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B159" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C159">
-        <v>625</v>
+        <v>898.15</v>
       </c>
       <c r="D159">
         <v>20544</v>
       </c>
       <c r="E159">
-        <v>5.4999999999999997E-3</v>
+        <v>5.5000000000000003E-8</v>
       </c>
       <c r="F159">
         <v>78</v>
@@ -4593,19 +4599,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B160" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C160">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D160">
         <v>127.4</v>
       </c>
       <c r="E160">
-        <v>3.54</v>
+        <v>3.54E-5</v>
       </c>
       <c r="F160">
         <v>216</v>
@@ -4619,19 +4625,19 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B161" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C161">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D161">
         <v>129.9</v>
       </c>
       <c r="E161">
-        <v>5.55</v>
+        <v>5.5500000000000001E-5</v>
       </c>
       <c r="F161">
         <v>216</v>
@@ -4645,19 +4651,19 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B162" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C162">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D162">
         <v>364.1</v>
       </c>
       <c r="E162">
-        <v>1.77</v>
+        <v>1.77E-5</v>
       </c>
       <c r="F162">
         <v>177</v>
@@ -4671,19 +4677,19 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B163" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C163">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D163">
         <v>1026.5999999999999</v>
       </c>
       <c r="E163">
-        <v>0.70899999999999996</v>
+        <v>7.0899999999999999E-6</v>
       </c>
       <c r="F163">
         <v>157</v>
@@ -4697,19 +4703,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C164">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D164">
         <v>1050.3</v>
       </c>
       <c r="E164">
-        <v>0.85199999999999998</v>
+        <v>8.5199999999999997E-6</v>
       </c>
       <c r="F164">
         <v>157</v>
@@ -4723,19 +4729,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B165" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C165">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D165">
         <v>9658.6</v>
       </c>
       <c r="E165">
-        <v>0.10299999999999999</v>
+        <v>1.0300000000000001E-6</v>
       </c>
       <c r="F165">
         <v>108</v>
@@ -4749,19 +4755,19 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B166" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C166">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D166">
         <v>31197.5</v>
       </c>
       <c r="E166">
-        <v>3.5900000000000001E-2</v>
+        <v>3.5900000000000003E-7</v>
       </c>
       <c r="F166">
         <v>88</v>
@@ -4775,19 +4781,19 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B167" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C167">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D167">
         <v>65232</v>
       </c>
       <c r="E167">
-        <v>1.6500000000000001E-2</v>
+        <v>1.6500000000000001E-7</v>
       </c>
       <c r="F167">
         <v>69</v>
@@ -4801,19 +4807,19 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B168" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C168">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D168">
         <v>128354.6</v>
       </c>
       <c r="E168">
-        <v>1.2200000000000001E-2</v>
+        <v>1.2200000000000001E-7</v>
       </c>
       <c r="F168">
         <v>61</v>
@@ -4827,19 +4833,19 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B169" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C169">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D169">
         <v>133748</v>
       </c>
       <c r="E169">
-        <v>6.1799999999999997E-3</v>
+        <v>6.1799999999999998E-8</v>
       </c>
       <c r="F169">
         <v>53</v>
@@ -4850,19 +4856,19 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B170" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C170">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D170">
         <v>101710</v>
       </c>
       <c r="E170">
-        <v>2.9199999999999999E-3</v>
+        <v>2.92E-8</v>
       </c>
       <c r="F170">
         <v>41</v>
@@ -4876,19 +4882,19 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B171" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C171">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D171">
         <v>91.6</v>
       </c>
       <c r="E171">
-        <v>25.5</v>
+        <v>2.5500000000000002E-4</v>
       </c>
       <c r="F171">
         <v>157</v>
@@ -4902,19 +4908,19 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B172" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C172">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D172">
         <v>83.9</v>
       </c>
       <c r="E172">
-        <v>22.7</v>
+        <v>2.2700000000000002E-4</v>
       </c>
       <c r="F172">
         <v>157</v>
@@ -4928,19 +4934,19 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B173" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C173">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D173">
         <v>263.2</v>
       </c>
       <c r="E173">
-        <v>2.64</v>
+        <v>2.6400000000000005E-5</v>
       </c>
       <c r="F173">
         <v>137</v>
@@ -4954,19 +4960,19 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B174" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C174">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D174">
         <v>1677.8</v>
       </c>
       <c r="E174">
-        <v>0.20799999999999999</v>
+        <v>2.08E-6</v>
       </c>
       <c r="F174">
         <v>98</v>
@@ -4980,19 +4986,19 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B175" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C175">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D175">
         <v>1391.6</v>
       </c>
       <c r="E175">
-        <v>0.379</v>
+        <v>3.7900000000000001E-6</v>
       </c>
       <c r="F175">
         <v>98</v>
@@ -5006,19 +5012,19 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B176" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C176">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D176">
         <v>5672.7</v>
       </c>
       <c r="E176">
-        <v>0.13900000000000001</v>
+        <v>1.3900000000000002E-6</v>
       </c>
       <c r="F176">
         <v>78</v>
@@ -5032,19 +5038,19 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C177">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D177">
         <v>21449.4</v>
       </c>
       <c r="E177">
-        <v>5.6300000000000003E-2</v>
+        <v>5.6300000000000005E-7</v>
       </c>
       <c r="F177">
         <v>61</v>
@@ -5058,19 +5064,19 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B178" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C178">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D178">
         <v>79089.3</v>
       </c>
       <c r="E178">
-        <v>2.4E-2</v>
+        <v>2.4000000000000003E-7</v>
       </c>
       <c r="F178">
         <v>47</v>
@@ -5084,19 +5090,19 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B179" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C179">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D179">
         <v>95542.3</v>
       </c>
       <c r="E179">
-        <v>2.01E-2</v>
+        <v>2.0100000000000001E-7</v>
       </c>
       <c r="F179">
         <v>41</v>
@@ -5110,19 +5116,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B180" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C180">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D180">
         <v>113924</v>
       </c>
       <c r="E180">
-        <v>8.6499999999999997E-3</v>
+        <v>8.65E-8</v>
       </c>
       <c r="F180">
         <v>33</v>
@@ -5136,19 +5142,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B181" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C181">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D181">
         <v>109088</v>
       </c>
       <c r="E181">
-        <v>3.0300000000000001E-3</v>
+        <v>3.0300000000000007E-8</v>
       </c>
       <c r="F181">
         <v>24</v>
@@ -5162,19 +5168,19 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B182" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C182">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D182">
         <v>171.9</v>
       </c>
       <c r="E182">
-        <v>3.32</v>
+        <v>3.3200000000000001E-5</v>
       </c>
       <c r="F182">
         <v>98</v>
@@ -5188,19 +5194,19 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B183" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C183">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D183">
         <v>174.2</v>
       </c>
       <c r="E183">
-        <v>3.51</v>
+        <v>3.5099999999999999E-5</v>
       </c>
       <c r="F183">
         <v>98</v>
@@ -5214,19 +5220,19 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B184" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C184">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D184">
         <v>679.1</v>
       </c>
       <c r="E184">
-        <v>1.51</v>
+        <v>1.5100000000000001E-5</v>
       </c>
       <c r="F184">
         <v>78</v>
@@ -5240,19 +5246,19 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B185" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C185">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D185">
         <v>7408.1</v>
       </c>
       <c r="E185">
-        <v>0.152</v>
+        <v>1.5200000000000001E-6</v>
       </c>
       <c r="F185">
         <v>47</v>
@@ -5266,19 +5272,19 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B186" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C186">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D186">
         <v>11218.4</v>
       </c>
       <c r="E186">
-        <v>7.9200000000000007E-2</v>
+        <v>7.920000000000001E-7</v>
       </c>
       <c r="F186">
         <v>37</v>
@@ -5292,19 +5298,19 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B187" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C187">
-        <v>775</v>
+        <v>1048.1500000000001</v>
       </c>
       <c r="D187">
         <v>3589.7</v>
       </c>
       <c r="E187">
-        <v>0.26500000000000001</v>
+        <v>2.6500000000000005E-6</v>
       </c>
       <c r="F187">
         <v>41</v>
@@ -5318,19 +5324,19 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C188">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D188">
         <v>267.60000000000002</v>
       </c>
       <c r="E188">
-        <v>0.70799999999999996</v>
+        <v>7.08E-6</v>
       </c>
       <c r="F188">
         <v>588</v>
@@ -5341,19 +5347,19 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C189">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D189">
         <v>1296.0999999999999</v>
       </c>
       <c r="E189">
-        <v>0.86099999999999999</v>
+        <v>8.6100000000000006E-6</v>
       </c>
       <c r="F189">
         <v>530</v>
@@ -5367,19 +5373,19 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C190">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D190">
         <v>7350.2</v>
       </c>
       <c r="E190">
-        <v>7.5399999999999995E-2</v>
+        <v>7.54E-7</v>
       </c>
       <c r="F190">
         <v>490</v>
@@ -5393,19 +5399,19 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C191">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D191">
         <v>13400.7</v>
       </c>
       <c r="E191">
-        <v>5.5500000000000001E-2</v>
+        <v>5.5500000000000009E-7</v>
       </c>
       <c r="F191">
         <v>471</v>
@@ -5419,19 +5425,19 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C192">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D192">
         <v>46117.5</v>
       </c>
       <c r="E192">
-        <v>4.2599999999999999E-3</v>
+        <v>4.2600000000000004E-8</v>
       </c>
       <c r="F192">
         <v>431</v>
@@ -5445,19 +5451,19 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C193">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D193">
         <v>65497.1</v>
       </c>
       <c r="E193">
-        <v>3.1700000000000001E-3</v>
+        <v>3.1700000000000006E-8</v>
       </c>
       <c r="F193">
         <v>412</v>
@@ -5471,19 +5477,19 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C194">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D194">
         <v>713.2</v>
       </c>
       <c r="E194">
-        <v>1.92</v>
+        <v>1.9200000000000003E-5</v>
       </c>
       <c r="F194">
         <v>471</v>
@@ -5494,19 +5500,19 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C195">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D195">
         <v>2878.2</v>
       </c>
       <c r="E195">
-        <v>0.154</v>
+        <v>1.5400000000000001E-6</v>
       </c>
       <c r="F195">
         <v>412</v>
@@ -5520,19 +5526,19 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C196">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D196">
         <v>7962.6</v>
       </c>
       <c r="E196">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4500000000000007E-7</v>
       </c>
       <c r="F196">
         <v>333</v>
@@ -5546,19 +5552,19 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C197">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D197">
         <v>32086.1</v>
       </c>
       <c r="E197">
-        <v>1.6199999999999999E-2</v>
+        <v>1.6199999999999999E-7</v>
       </c>
       <c r="F197">
         <v>265</v>
@@ -5572,19 +5578,19 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C198">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D198">
         <v>72802.7</v>
       </c>
       <c r="E198">
-        <v>9.0500000000000008E-3</v>
+        <v>9.050000000000001E-8</v>
       </c>
       <c r="F198">
         <v>235</v>
@@ -5598,19 +5604,19 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C199">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D199">
         <v>369.3</v>
       </c>
       <c r="E199">
-        <v>4.46</v>
+        <v>4.4600000000000007E-5</v>
       </c>
       <c r="F199">
         <v>373</v>
@@ -5624,19 +5630,19 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C200">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D200">
         <v>3306</v>
       </c>
       <c r="E200">
-        <v>0.30599999999999999</v>
+        <v>3.0600000000000003E-6</v>
       </c>
       <c r="F200">
         <v>265</v>
@@ -5650,19 +5656,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C201">
-        <v>650</v>
+        <v>923.15</v>
       </c>
       <c r="D201">
         <v>23837</v>
       </c>
       <c r="E201">
-        <v>1.8100000000000002E-2</v>
+        <v>1.8100000000000002E-7</v>
       </c>
       <c r="F201">
         <v>177</v>
@@ -5676,19 +5682,19 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C202">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D202">
         <v>240.9</v>
       </c>
       <c r="E202">
-        <v>7.73</v>
+        <v>7.7300000000000009E-5</v>
       </c>
       <c r="F202">
         <v>265</v>
@@ -5702,19 +5708,19 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C203">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D203">
         <v>1667.4</v>
       </c>
       <c r="E203">
-        <v>0.66700000000000004</v>
+        <v>6.6700000000000005E-6</v>
       </c>
       <c r="F203">
         <v>177</v>
@@ -5728,19 +5734,19 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C204">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D204">
         <v>11628.9</v>
       </c>
       <c r="E204">
-        <v>0.20100000000000001</v>
+        <v>2.0100000000000002E-6</v>
       </c>
       <c r="F204">
         <v>118</v>
@@ -5754,19 +5760,19 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C205">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D205">
         <v>275.60000000000002</v>
       </c>
       <c r="E205">
-        <v>5.21</v>
+        <v>5.2100000000000006E-5</v>
       </c>
       <c r="F205">
         <v>588</v>
@@ -5777,19 +5783,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C206">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D206">
         <v>9906.6</v>
       </c>
       <c r="E206">
-        <v>1.37E-2</v>
+        <v>1.3700000000000002E-7</v>
       </c>
       <c r="F206">
         <v>490</v>
@@ -5803,19 +5809,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C207">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D207">
         <v>21158.1</v>
       </c>
       <c r="E207">
-        <v>1.41E-2</v>
+        <v>1.4100000000000001E-7</v>
       </c>
       <c r="F207">
         <v>171</v>
@@ -5829,19 +5835,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C208">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D208">
         <v>36907.800000000003</v>
       </c>
       <c r="E208">
-        <v>5.1599999999999997E-3</v>
+        <v>5.1599999999999999E-8</v>
       </c>
       <c r="F208">
         <v>431</v>
@@ -5855,19 +5861,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C209">
-        <v>550</v>
+        <v>823.15</v>
       </c>
       <c r="D209">
         <v>47955.6</v>
       </c>
       <c r="E209">
-        <v>2.8500000000000001E-3</v>
+        <v>2.8500000000000004E-8</v>
       </c>
       <c r="F209">
         <v>412</v>
@@ -5881,19 +5887,19 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C210">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D210">
         <v>450.3</v>
       </c>
       <c r="E210">
-        <v>1.48</v>
+        <v>1.4800000000000001E-5</v>
       </c>
       <c r="F210">
         <v>471</v>
@@ -5904,19 +5910,19 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C211">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D211">
         <v>2782.3</v>
       </c>
       <c r="E211">
-        <v>0.122</v>
+        <v>1.2200000000000002E-6</v>
       </c>
       <c r="F211">
         <v>412</v>
@@ -5930,19 +5936,19 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C212">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D212">
         <v>13690.1</v>
       </c>
       <c r="E212">
-        <v>2.1299999999999999E-2</v>
+        <v>2.1300000000000001E-7</v>
       </c>
       <c r="F212">
         <v>333</v>
@@ -5956,19 +5962,19 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C213">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D213">
         <v>56282.400000000001</v>
       </c>
       <c r="E213">
-        <v>5.96E-3</v>
+        <v>5.9600000000000004E-8</v>
       </c>
       <c r="F213">
         <v>265</v>
@@ -5982,19 +5988,19 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C214">
-        <v>600</v>
+        <v>873.15</v>
       </c>
       <c r="D214">
         <v>114570</v>
       </c>
       <c r="E214">
-        <v>3.5000000000000001E-3</v>
+        <v>3.5000000000000002E-8</v>
       </c>
       <c r="F214">
         <v>235</v>
@@ -6008,19 +6014,19 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B215" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C215">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D215">
         <v>10822.5</v>
       </c>
       <c r="E215">
-        <v>0.14299999999999999</v>
+        <v>1.4300000000000001E-6</v>
       </c>
       <c r="F215">
         <v>157</v>
@@ -6034,19 +6040,19 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B216" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C216">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D216">
         <v>33793</v>
       </c>
       <c r="E216">
-        <v>1.9800000000000002E-2</v>
+        <v>1.9800000000000003E-7</v>
       </c>
       <c r="F216">
         <v>137</v>
@@ -6060,16 +6066,16 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B217" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C217">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="E217">
-        <v>6.8099999999999994E-2</v>
+        <v>6.8100000000000002E-7</v>
       </c>
       <c r="F217">
         <v>118</v>
@@ -6080,19 +6086,19 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C218">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D218">
         <v>13441</v>
       </c>
       <c r="E218">
-        <v>4.6899999999999997E-2</v>
+        <v>4.6900000000000003E-7</v>
       </c>
       <c r="F218">
         <v>118</v>
@@ -6106,19 +6112,19 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B219" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C219">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D219">
         <v>20172.3</v>
       </c>
       <c r="E219">
-        <v>4.9399999999999999E-2</v>
+        <v>4.9400000000000006E-7</v>
       </c>
       <c r="F219">
         <v>98</v>
@@ -6132,19 +6138,19 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B220" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C220">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D220">
         <v>39549.9</v>
       </c>
       <c r="E220">
-        <v>1.41E-2</v>
+        <v>1.4100000000000001E-7</v>
       </c>
       <c r="F220">
         <v>88</v>
@@ -6158,19 +6164,19 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B221" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C221">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D221">
         <v>5537.6</v>
       </c>
       <c r="E221">
-        <v>8.7999999999999995E-2</v>
+        <v>8.8000000000000004E-7</v>
       </c>
       <c r="F221">
         <v>78</v>
@@ -6184,19 +6190,19 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B222" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C222">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D222">
         <v>32809.199999999997</v>
       </c>
       <c r="E222">
-        <v>1.9900000000000001E-2</v>
+        <v>1.9900000000000002E-7</v>
       </c>
       <c r="F222">
         <v>61</v>
@@ -6210,19 +6216,19 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B223" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C223">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D223">
         <v>28895.200000000001</v>
       </c>
       <c r="E223">
-        <v>1.9099999999999999E-2</v>
+        <v>1.91E-7</v>
       </c>
       <c r="F223">
         <v>47</v>
@@ -6236,19 +6242,19 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B224" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C224">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D224">
         <v>15460.4</v>
       </c>
       <c r="E224">
-        <v>4.7100000000000003E-2</v>
+        <v>4.7100000000000008E-7</v>
       </c>
       <c r="F224">
         <v>41</v>
@@ -6262,19 +6268,19 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B225" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C225">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D225">
         <v>11511.9</v>
       </c>
       <c r="E225">
-        <v>0.14699999999999999</v>
+        <v>1.4700000000000001E-6</v>
       </c>
       <c r="F225">
         <v>157</v>
@@ -6288,19 +6294,19 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B226" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C226">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D226">
         <v>8619.7999999999993</v>
       </c>
       <c r="E226">
-        <v>6.8099999999999994E-2</v>
+        <v>6.8100000000000002E-7</v>
       </c>
       <c r="F226">
         <v>137</v>
@@ -6314,19 +6320,19 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B227" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C227">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D227">
         <v>34860.6</v>
       </c>
       <c r="E227">
-        <v>2.2700000000000001E-2</v>
+        <v>2.2700000000000003E-7</v>
       </c>
       <c r="F227">
         <v>118</v>
@@ -6340,19 +6346,19 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B228" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C228">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D228">
         <v>11000.8</v>
       </c>
       <c r="E228">
-        <v>8.1199999999999994E-2</v>
+        <v>8.1200000000000002E-7</v>
       </c>
       <c r="F228">
         <v>118</v>
@@ -6366,19 +6372,19 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B229" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C229">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D229">
         <v>23942.6</v>
       </c>
       <c r="E229">
-        <v>4.2999999999999997E-2</v>
+        <v>4.3000000000000001E-7</v>
       </c>
       <c r="F229">
         <v>98</v>
@@ -6392,19 +6398,19 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B230" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C230">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D230">
         <v>28267.200000000001</v>
       </c>
       <c r="E230">
-        <v>2.35E-2</v>
+        <v>2.3500000000000003E-7</v>
       </c>
       <c r="F230">
         <v>88</v>
@@ -6418,19 +6424,19 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B231" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C231">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D231">
         <v>2345</v>
       </c>
       <c r="E231">
-        <v>0.371</v>
+        <v>3.7100000000000005E-6</v>
       </c>
       <c r="F231">
         <v>98</v>
@@ -6444,19 +6450,19 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B232" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C232">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D232">
         <v>7882.8</v>
       </c>
       <c r="E232">
-        <v>3.6600000000000001E-2</v>
+        <v>3.6600000000000002E-7</v>
       </c>
       <c r="F232">
         <v>78</v>
@@ -6470,19 +6476,19 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B233" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C233">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D233">
         <v>18567.400000000001</v>
       </c>
       <c r="E233">
-        <v>3.7100000000000001E-2</v>
+        <v>3.7100000000000003E-7</v>
       </c>
       <c r="F233">
         <v>53</v>
@@ -6496,19 +6502,19 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B234" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C234">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D234">
         <v>3029.7</v>
       </c>
       <c r="E234">
-        <v>0.248</v>
+        <v>2.4800000000000004E-6</v>
       </c>
       <c r="F234">
         <v>61</v>
@@ -6522,19 +6528,19 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B235" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C235">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D235">
         <v>3870.3</v>
       </c>
       <c r="E235">
-        <v>2.63E-2</v>
+        <v>2.6300000000000001E-7</v>
       </c>
       <c r="F235">
         <v>47</v>
@@ -6548,19 +6554,19 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B236" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C236">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D236">
         <v>13001.4</v>
       </c>
       <c r="E236">
-        <v>8.3299999999999999E-2</v>
+        <v>8.3300000000000001E-7</v>
       </c>
       <c r="F236">
         <v>37</v>
@@ -6574,19 +6580,19 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B237" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C237">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D237">
         <v>15989</v>
       </c>
       <c r="E237">
-        <v>6.1199999999999997E-2</v>
+        <v>6.1200000000000003E-7</v>
       </c>
       <c r="F237">
         <v>31</v>
@@ -6600,19 +6606,19 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B238" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C238">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D238">
         <v>3514.7</v>
       </c>
       <c r="E238">
-        <v>0.4</v>
+        <v>4.0000000000000007E-6</v>
       </c>
       <c r="F238">
         <v>157</v>
@@ -6626,19 +6632,19 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B239" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C239">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D239">
         <v>7122.4</v>
       </c>
       <c r="E239">
-        <v>0.25</v>
+        <v>2.5000000000000002E-6</v>
       </c>
       <c r="F239">
         <v>137</v>
@@ -6652,19 +6658,19 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B240" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C240">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D240">
         <v>52149</v>
       </c>
       <c r="E240">
-        <v>9.6900000000000007E-3</v>
+        <v>9.6900000000000014E-8</v>
       </c>
       <c r="F240">
         <v>108</v>
@@ -6678,19 +6684,19 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B241" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C241">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D241">
         <v>7420.8</v>
       </c>
       <c r="E241">
-        <v>0.11799999999999999</v>
+        <v>1.1800000000000001E-6</v>
       </c>
       <c r="F241">
         <v>118</v>
@@ -6704,19 +6710,19 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B242" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C242">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D242">
         <v>14076.8</v>
       </c>
       <c r="E242">
-        <v>5.8799999999999998E-2</v>
+        <v>5.8800000000000002E-7</v>
       </c>
       <c r="F242">
         <v>98</v>
@@ -6730,19 +6736,19 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B243" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C243">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D243">
         <v>41418.300000000003</v>
       </c>
       <c r="E243">
-        <v>1.0500000000000001E-2</v>
+        <v>1.0500000000000001E-7</v>
       </c>
       <c r="F243">
         <v>78</v>
@@ -6756,19 +6762,19 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B244" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C244">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D244">
         <v>4302.2</v>
       </c>
       <c r="E244">
-        <v>7.2300000000000003E-2</v>
+        <v>7.2300000000000011E-7</v>
       </c>
       <c r="F244">
         <v>98</v>
@@ -6782,16 +6788,16 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B245" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C245">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="E245">
-        <v>5.96E-3</v>
+        <v>5.9600000000000004E-8</v>
       </c>
       <c r="F245">
         <v>61</v>
@@ -6802,19 +6808,19 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B246" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C246">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D246">
         <v>1736.3</v>
       </c>
       <c r="E246">
-        <v>0.80500000000000005</v>
+        <v>8.0500000000000009E-6</v>
       </c>
       <c r="F246">
         <v>157</v>
@@ -6828,19 +6834,19 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B247" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C247">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D247">
         <v>16837.7</v>
       </c>
       <c r="E247">
-        <v>4.9500000000000002E-2</v>
+        <v>4.9500000000000003E-7</v>
       </c>
       <c r="F247">
         <v>137</v>
@@ -6854,19 +6860,19 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B248" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C248">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D248">
         <v>2639</v>
       </c>
       <c r="E248">
-        <v>0.32400000000000001</v>
+        <v>3.2400000000000003E-6</v>
       </c>
       <c r="F248">
         <v>98</v>
@@ -6880,19 +6886,19 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B249" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C249">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D249">
         <v>14917.2</v>
       </c>
       <c r="E249">
-        <v>9.7799999999999998E-2</v>
+        <v>9.78E-7</v>
       </c>
       <c r="F249">
         <v>69</v>
@@ -6906,19 +6912,19 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B250" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C250">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D250">
         <v>3098.2</v>
       </c>
       <c r="E250">
-        <v>0.215</v>
+        <v>2.1500000000000002E-6</v>
       </c>
       <c r="F250">
         <v>61</v>
@@ -6932,19 +6938,19 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B251" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C251">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D251">
         <v>15278.3</v>
       </c>
       <c r="E251">
-        <v>5.9200000000000003E-2</v>
+        <v>5.9200000000000011E-7</v>
       </c>
       <c r="F251">
         <v>47</v>
@@ -6958,19 +6964,19 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B252" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C252">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D252">
         <v>41690.6</v>
       </c>
       <c r="E252">
-        <v>1.3899999999999999E-2</v>
+        <v>1.3900000000000001E-7</v>
       </c>
       <c r="F252">
         <v>37</v>
@@ -6984,19 +6990,19 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B253" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C253">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D253">
         <v>1700.3</v>
       </c>
       <c r="E253">
-        <v>0.36899999999999999</v>
+        <v>3.6900000000000002E-6</v>
       </c>
       <c r="F253">
         <v>47</v>
@@ -7010,19 +7016,19 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B254" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C254">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D254">
         <v>4260.5</v>
       </c>
       <c r="E254">
-        <v>0.16300000000000001</v>
+        <v>1.6300000000000003E-6</v>
       </c>
       <c r="F254">
         <v>37</v>
@@ -7036,19 +7042,19 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B255" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C255">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D255">
         <v>12062.8</v>
       </c>
       <c r="E255">
-        <v>4.48E-2</v>
+        <v>4.4800000000000004E-7</v>
       </c>
       <c r="F255">
         <v>29</v>
@@ -7062,19 +7068,19 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B256" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C256">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D256">
         <v>17485.3</v>
       </c>
       <c r="E256">
-        <v>5.2999999999999999E-2</v>
+        <v>5.3000000000000001E-7</v>
       </c>
       <c r="F256">
         <v>157</v>
@@ -7088,19 +7094,19 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B257" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C257">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D257">
         <v>14395.6</v>
       </c>
       <c r="E257">
-        <v>2.9399999999999999E-2</v>
+        <v>2.9400000000000001E-7</v>
       </c>
       <c r="F257">
         <v>118</v>
@@ -7114,19 +7120,19 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B258" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C258">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D258">
         <v>25632.799999999999</v>
       </c>
       <c r="E258">
-        <v>2.9399999999999999E-2</v>
+        <v>2.9400000000000001E-7</v>
       </c>
       <c r="F258">
         <v>98</v>
@@ -7140,19 +7146,19 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B259" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C259">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D259">
         <v>31744.400000000001</v>
       </c>
       <c r="E259">
-        <v>1.03E-2</v>
+        <v>1.0300000000000001E-7</v>
       </c>
       <c r="F259">
         <v>88</v>
@@ -7166,19 +7172,19 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B260" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C260">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D260">
         <v>8511.2000000000007</v>
       </c>
       <c r="E260">
-        <v>4.3799999999999999E-2</v>
+        <v>4.3800000000000003E-7</v>
       </c>
       <c r="F260">
         <v>78</v>
@@ -7192,19 +7198,19 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B261" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C261">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D261">
         <v>18247.400000000001</v>
       </c>
       <c r="E261">
-        <v>2.7099999999999999E-2</v>
+        <v>2.7100000000000003E-7</v>
       </c>
       <c r="F261">
         <v>51</v>
@@ -7218,19 +7224,19 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B262" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C262">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D262">
         <v>813.9</v>
       </c>
       <c r="E262">
-        <v>1.88</v>
+        <v>1.88E-5</v>
       </c>
       <c r="F262">
         <v>216</v>
@@ -7244,19 +7250,19 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B263" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C263">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D263">
         <v>4405.8999999999996</v>
       </c>
       <c r="E263">
-        <v>0.51300000000000001</v>
+        <v>5.1300000000000009E-6</v>
       </c>
       <c r="F263">
         <v>157</v>
@@ -7270,19 +7276,19 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B264" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C264">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D264">
         <v>9587.7999999999993</v>
       </c>
       <c r="E264">
-        <v>0.215</v>
+        <v>2.1500000000000002E-6</v>
       </c>
       <c r="F264">
         <v>137</v>
@@ -7296,19 +7302,19 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B265" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C265">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D265">
         <v>42705.5</v>
       </c>
       <c r="E265">
-        <v>5.11E-2</v>
+        <v>5.1100000000000006E-7</v>
       </c>
       <c r="F265">
         <v>108</v>
@@ -7322,19 +7328,19 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B266" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C266">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D266">
         <v>7323.4</v>
       </c>
       <c r="E266">
-        <v>0.13800000000000001</v>
+        <v>1.3800000000000001E-6</v>
       </c>
       <c r="F266">
         <v>118</v>
@@ -7348,19 +7354,19 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B267" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C267">
-        <v>9500</v>
+        <v>9773.15</v>
       </c>
       <c r="D267">
         <v>17178.099999999999</v>
       </c>
       <c r="E267">
-        <v>6.2799999999999995E-2</v>
+        <v>6.2799999999999996E-7</v>
       </c>
       <c r="F267">
         <v>98</v>
@@ -7374,19 +7380,19 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B268" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C268">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D268">
         <v>3214.7</v>
       </c>
       <c r="E268">
-        <v>0.33700000000000002</v>
+        <v>3.3700000000000003E-6</v>
       </c>
       <c r="F268">
         <v>98</v>
@@ -7400,19 +7406,19 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B269" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C269">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D269">
         <v>9409</v>
       </c>
       <c r="E269">
-        <v>8.0399999999999999E-2</v>
+        <v>8.0400000000000005E-7</v>
       </c>
       <c r="F269">
         <v>78</v>
@@ -7426,19 +7432,19 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B270" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C270">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D270">
         <v>23639.4</v>
       </c>
       <c r="E270">
-        <v>3.9800000000000002E-2</v>
+        <v>3.9800000000000004E-7</v>
       </c>
       <c r="F270">
         <v>61</v>
@@ -7452,19 +7458,19 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B271" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C271">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D271">
         <v>2319.9</v>
       </c>
       <c r="E271">
-        <v>0.72399999999999998</v>
+        <v>7.2400000000000001E-6</v>
       </c>
       <c r="F271">
         <v>157</v>
@@ -7478,19 +7484,19 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B272" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C272">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D272">
         <v>12278</v>
       </c>
       <c r="E272">
-        <v>6.4899999999999999E-2</v>
+        <v>6.4900000000000005E-7</v>
       </c>
       <c r="F272">
         <v>137</v>
@@ -7504,19 +7510,19 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B273" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C273">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D273">
         <v>33178.199999999997</v>
       </c>
       <c r="E273">
-        <v>3.0200000000000001E-2</v>
+        <v>3.0200000000000003E-7</v>
       </c>
       <c r="F273">
         <v>118</v>
@@ -7530,19 +7536,19 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B274" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C274">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D274">
         <v>89830</v>
       </c>
       <c r="E274">
-        <v>5.28E-3</v>
+        <v>5.2800000000000003E-8</v>
       </c>
       <c r="F274">
         <v>98</v>
@@ -7556,19 +7562,19 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B275" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C275">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D275">
         <v>2341.4</v>
       </c>
       <c r="E275">
-        <v>0.53600000000000003</v>
+        <v>5.3600000000000004E-6</v>
       </c>
       <c r="F275">
         <v>98</v>
@@ -7582,19 +7588,19 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B276" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C276">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D276">
         <v>4100</v>
       </c>
       <c r="E276">
-        <v>0.318</v>
+        <v>3.1800000000000005E-6</v>
       </c>
       <c r="F276">
         <v>88</v>
@@ -7608,19 +7614,19 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B277" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C277">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D277">
         <v>1297.4000000000001</v>
       </c>
       <c r="E277">
-        <v>0.40899999999999997</v>
+        <v>4.0899999999999998E-6</v>
       </c>
       <c r="F277">
         <v>78</v>
@@ -7634,19 +7640,19 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B278" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C278">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D278">
         <v>17961.8</v>
       </c>
       <c r="E278">
-        <v>1.7999999999999999E-2</v>
+        <v>1.8E-7</v>
       </c>
       <c r="F278">
         <v>61</v>
@@ -7660,19 +7666,19 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B279" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C279">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D279">
         <v>7892.3</v>
       </c>
       <c r="E279">
-        <v>4.07E-2</v>
+        <v>4.0700000000000003E-7</v>
       </c>
       <c r="F279">
         <v>47</v>
@@ -7686,16 +7692,16 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B280" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C280">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="E280">
-        <v>6.0199999999999997E-2</v>
+        <v>6.0200000000000002E-7</v>
       </c>
       <c r="F280">
         <v>33</v>
@@ -7706,19 +7712,19 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B281" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C281">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D281">
         <v>16553.400000000001</v>
       </c>
       <c r="E281">
-        <v>6.2899999999999998E-2</v>
+        <v>6.2900000000000003E-7</v>
       </c>
       <c r="F281">
         <v>157</v>
@@ -7732,19 +7738,19 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B282" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C282">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D282">
         <v>25541.1</v>
       </c>
       <c r="E282">
-        <v>2.52E-2</v>
+        <v>2.5200000000000003E-7</v>
       </c>
       <c r="F282">
         <v>137</v>
@@ -7758,19 +7764,19 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B283" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C283">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D283">
         <v>7881.8</v>
       </c>
       <c r="E283">
-        <v>9.8699999999999996E-2</v>
+        <v>9.8700000000000004E-7</v>
       </c>
       <c r="F283">
         <v>118</v>
@@ -7784,19 +7790,19 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B284" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C284">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D284">
         <v>15840.6</v>
       </c>
       <c r="E284">
-        <v>5.6399999999999999E-2</v>
+        <v>5.6400000000000002E-7</v>
       </c>
       <c r="F284">
         <v>98</v>
@@ -7810,19 +7816,19 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B285" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C285">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D285">
         <v>38769.1</v>
       </c>
       <c r="E285">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92E-7</v>
       </c>
       <c r="F285">
         <v>88</v>
@@ -7836,19 +7842,19 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B286" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C286">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D286">
         <v>8479.2999999999993</v>
       </c>
       <c r="E286">
-        <v>7.9699999999999993E-2</v>
+        <v>7.9699999999999995E-7</v>
       </c>
       <c r="F286">
         <v>78</v>
@@ -7862,19 +7868,19 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B287" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C287">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D287">
         <v>34824.300000000003</v>
       </c>
       <c r="E287">
-        <v>1.12E-2</v>
+        <v>1.1200000000000001E-7</v>
       </c>
       <c r="F287">
         <v>61</v>
@@ -7888,19 +7894,19 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B288" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C288">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D288">
         <v>12629.9</v>
       </c>
       <c r="E288">
-        <v>6.5799999999999997E-2</v>
+        <v>6.5799999999999999E-7</v>
       </c>
       <c r="F288">
         <v>47</v>
@@ -7914,19 +7920,19 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B289" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C289">
-        <v>1000</v>
+        <v>1273.1500000000001</v>
       </c>
       <c r="D289">
         <v>47538.6</v>
       </c>
       <c r="E289">
-        <v>8.7200000000000003E-3</v>
+        <v>8.7200000000000013E-8</v>
       </c>
       <c r="F289">
         <v>37</v>
@@ -7940,19 +7946,19 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B290" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C290">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D290">
         <v>3162.4</v>
       </c>
       <c r="E290">
-        <v>0.249</v>
+        <v>2.4900000000000003E-6</v>
       </c>
       <c r="F290">
         <v>412</v>
@@ -7966,19 +7972,19 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C291">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D291">
         <v>6833</v>
       </c>
       <c r="E291">
-        <v>0.121</v>
+        <v>1.2100000000000001E-6</v>
       </c>
       <c r="F291">
         <v>373</v>
@@ -7992,19 +7998,19 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C292">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D292">
         <v>21051</v>
       </c>
       <c r="E292">
-        <v>2.29E-2</v>
+        <v>2.2900000000000003E-7</v>
       </c>
       <c r="F292">
         <v>333</v>
@@ -8018,19 +8024,19 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B293" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C293">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D293">
         <v>66840.5</v>
       </c>
       <c r="E293">
-        <v>7.9500000000000005E-3</v>
+        <v>7.9500000000000017E-8</v>
       </c>
       <c r="F293">
         <v>294</v>
@@ -8044,19 +8050,19 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B294" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C294">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D294">
         <v>4758.5</v>
       </c>
       <c r="E294">
-        <v>0.185</v>
+        <v>1.8500000000000001E-6</v>
       </c>
       <c r="F294">
         <v>294</v>
@@ -8070,19 +8076,19 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B295" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C295">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D295">
         <v>11046.2</v>
       </c>
       <c r="E295">
-        <v>6.9000000000000006E-2</v>
+        <v>6.9000000000000006E-7</v>
       </c>
       <c r="F295">
         <v>265</v>
@@ -8096,19 +8102,19 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C296">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D296">
         <v>20594.5</v>
       </c>
       <c r="E296">
-        <v>5.5300000000000002E-2</v>
+        <v>5.5300000000000004E-7</v>
       </c>
       <c r="F296">
         <v>235</v>
@@ -8122,19 +8128,19 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C297">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D297">
         <v>55273.2</v>
       </c>
       <c r="E297">
-        <v>1.35E-2</v>
+        <v>1.35E-7</v>
       </c>
       <c r="F297">
         <v>196</v>
@@ -8148,19 +8154,19 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B298" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C298">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D298">
         <v>1632.4</v>
       </c>
       <c r="E298">
-        <v>0.81899999999999995</v>
+        <v>8.1899999999999995E-6</v>
       </c>
       <c r="F298">
         <v>235</v>
@@ -8174,19 +8180,19 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B299" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C299">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D299">
         <v>4365.7</v>
       </c>
       <c r="E299">
-        <v>0.25800000000000001</v>
+        <v>2.5800000000000003E-6</v>
       </c>
       <c r="F299">
         <v>196</v>
@@ -8200,19 +8206,19 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B300" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C300">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D300">
         <v>13144.8</v>
       </c>
       <c r="E300">
-        <v>7.5300000000000006E-2</v>
+        <v>7.5300000000000014E-7</v>
       </c>
       <c r="F300">
         <v>157</v>
@@ -8226,19 +8232,19 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B301" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C301">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D301">
         <v>23070.2</v>
       </c>
       <c r="E301">
-        <v>5.7299999999999997E-2</v>
+        <v>5.7300000000000006E-7</v>
       </c>
       <c r="F301">
         <v>137</v>
@@ -8252,19 +8258,19 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B302" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C302">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D302">
         <v>3988.1</v>
       </c>
       <c r="E302">
-        <v>0.32300000000000001</v>
+        <v>3.2300000000000004E-6</v>
       </c>
       <c r="F302">
         <v>118</v>
@@ -8278,19 +8284,19 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B303" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C303">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D303">
         <v>7499.6</v>
       </c>
       <c r="E303">
-        <v>0.13600000000000001</v>
+        <v>1.3600000000000001E-6</v>
       </c>
       <c r="F303">
         <v>98</v>
@@ -8304,19 +8310,19 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B304" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C304">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D304">
         <v>10549</v>
       </c>
       <c r="E304">
-        <v>0.1</v>
+        <v>1.0000000000000002E-6</v>
       </c>
       <c r="F304">
         <v>88</v>
@@ -8330,19 +8336,19 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B305" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C305">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D305">
         <v>26141.7</v>
       </c>
       <c r="E305">
-        <v>4.9500000000000002E-2</v>
+        <v>4.9500000000000003E-7</v>
       </c>
       <c r="F305">
         <v>69</v>
@@ -8356,19 +8362,19 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B306" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C306">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D306">
         <v>4415.3999999999996</v>
       </c>
       <c r="E306">
-        <v>0.27500000000000002</v>
+        <v>2.7500000000000004E-6</v>
       </c>
       <c r="F306">
         <v>412</v>
@@ -8382,19 +8388,19 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B307" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C307">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D307">
         <v>6539.8</v>
       </c>
       <c r="E307">
-        <v>0.16200000000000001</v>
+        <v>1.6200000000000002E-6</v>
       </c>
       <c r="F307">
         <v>373</v>
@@ -8408,19 +8414,19 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B308" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C308">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D308">
         <v>16002.2</v>
       </c>
       <c r="E308">
-        <v>5.96E-2</v>
+        <v>5.960000000000001E-7</v>
       </c>
       <c r="F308">
         <v>333</v>
@@ -8434,19 +8440,19 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B309" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C309">
-        <v>700</v>
+        <v>973.15</v>
       </c>
       <c r="D309">
         <v>28726</v>
       </c>
       <c r="E309">
-        <v>2.4E-2</v>
+        <v>2.4000000000000003E-7</v>
       </c>
       <c r="F309">
         <v>294</v>
@@ -8460,17 +8466,20 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B310" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C310">
-        <v>725</v>
+        <v>998.15</v>
       </c>
       <c r="D310">
         <v>695.4</v>
       </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
       <c r="F310">
         <v>412</v>
       </c>
@@ -8483,17 +8492,20 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B311" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C311">
-        <v>725</v>
+        <v>998.15</v>
       </c>
       <c r="D311">
         <v>1658.6</v>
       </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
       <c r="F311">
         <v>373</v>
       </c>
@@ -8506,19 +8518,19 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B312" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C312">
-        <v>725</v>
+        <v>998.15</v>
       </c>
       <c r="D312">
         <v>9395.2999999999993</v>
       </c>
       <c r="E312">
-        <v>0.14299999999999999</v>
+        <v>1.4300000000000001E-6</v>
       </c>
       <c r="F312">
         <v>294</v>
@@ -8532,19 +8544,19 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B313" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C313">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D313">
         <v>2972.6</v>
       </c>
       <c r="E313">
-        <v>0.46400000000000002</v>
+        <v>4.6400000000000005E-6</v>
       </c>
       <c r="F313">
         <v>294</v>
@@ -8558,19 +8570,19 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C314">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D314">
         <v>5630</v>
       </c>
       <c r="E314">
-        <v>0.23300000000000001</v>
+        <v>2.3300000000000001E-6</v>
       </c>
       <c r="F314">
         <v>265</v>
@@ -8584,19 +8596,19 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B315" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C315">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D315">
         <v>13909.1</v>
       </c>
       <c r="E315">
-        <v>7.1300000000000002E-2</v>
+        <v>7.130000000000001E-7</v>
       </c>
       <c r="F315">
         <v>235</v>
@@ -8610,19 +8622,19 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B316" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C316">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D316">
         <v>16924.400000000001</v>
       </c>
       <c r="E316">
-        <v>1.3599999999999999E-2</v>
+        <v>1.36E-7</v>
       </c>
       <c r="F316">
         <v>196</v>
@@ -8636,19 +8648,19 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B317" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C317">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D317">
         <v>1288.5</v>
       </c>
       <c r="E317">
-        <v>0.90600000000000003</v>
+        <v>9.0600000000000013E-6</v>
       </c>
       <c r="F317">
         <v>235</v>
@@ -8662,19 +8674,19 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B318" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C318">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D318">
         <v>4263.7</v>
       </c>
       <c r="E318">
-        <v>0.23699999999999999</v>
+        <v>2.3700000000000002E-6</v>
       </c>
       <c r="F318">
         <v>196</v>
@@ -8688,19 +8700,19 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B319" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C319">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D319">
         <v>12558.2</v>
       </c>
       <c r="E319">
-        <v>3.9899999999999998E-2</v>
+        <v>3.9900000000000001E-7</v>
       </c>
       <c r="F319">
         <v>157</v>
@@ -8714,19 +8726,19 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B320" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C320">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D320">
         <v>28414.799999999999</v>
       </c>
       <c r="E320">
-        <v>1.4200000000000001E-2</v>
+        <v>1.4200000000000003E-7</v>
       </c>
       <c r="F320">
         <v>137</v>
@@ -8740,19 +8752,19 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B321" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C321">
-        <v>825</v>
+        <v>1098.1500000000001</v>
       </c>
       <c r="D321">
         <v>264.60000000000002</v>
       </c>
       <c r="E321">
-        <v>6.02</v>
+        <v>6.02E-5</v>
       </c>
       <c r="F321">
         <v>235</v>
@@ -8766,19 +8778,19 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B322" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C322">
-        <v>825</v>
+        <v>1098.1500000000001</v>
       </c>
       <c r="D322">
         <v>1065.2</v>
       </c>
       <c r="E322">
-        <v>1.1599999999999999</v>
+        <v>1.1600000000000001E-5</v>
       </c>
       <c r="F322">
         <v>196</v>
@@ -8792,19 +8804,19 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B323" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C323">
-        <v>825</v>
+        <v>1098.1500000000001</v>
       </c>
       <c r="D323">
         <v>6636</v>
       </c>
       <c r="E323">
-        <v>0.123</v>
+        <v>1.2300000000000001E-6</v>
       </c>
       <c r="F323">
         <v>137</v>
@@ -8818,19 +8830,19 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B324" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C324">
-        <v>825</v>
+        <v>1098.1500000000001</v>
       </c>
       <c r="D324">
         <v>14601.8</v>
       </c>
       <c r="E324">
-        <v>4.6600000000000003E-2</v>
+        <v>4.6600000000000007E-7</v>
       </c>
       <c r="F324">
         <v>98</v>
@@ -8844,19 +8856,19 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B325" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C325">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D325">
         <v>511.9</v>
       </c>
       <c r="E325">
-        <v>3.4</v>
+        <v>3.4E-5</v>
       </c>
       <c r="F325">
         <v>177</v>
@@ -8870,19 +8882,19 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B326" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C326">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D326">
         <v>5218.3</v>
       </c>
       <c r="E326">
-        <v>0.112</v>
+        <v>1.1200000000000001E-6</v>
       </c>
       <c r="F326">
         <v>118</v>
@@ -8896,19 +8908,19 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B327" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C327">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D327">
         <v>9716.6</v>
       </c>
       <c r="E327">
-        <v>7.5200000000000003E-2</v>
+        <v>7.5200000000000006E-7</v>
       </c>
       <c r="F327">
         <v>98</v>
@@ -8922,19 +8934,19 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B328" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C328">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D328">
         <v>10108.4</v>
       </c>
       <c r="E328">
-        <v>9.64E-2</v>
+        <v>9.64E-7</v>
       </c>
       <c r="F328">
         <v>88</v>
@@ -8948,19 +8960,19 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B329" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C329">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D329">
         <v>16505</v>
       </c>
       <c r="E329">
-        <v>6.5299999999999997E-2</v>
+        <v>6.5300000000000004E-7</v>
       </c>
       <c r="F329">
         <v>69</v>
@@ -8974,19 +8986,19 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B330" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C330">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D330">
         <v>10596.3</v>
       </c>
       <c r="E330">
-        <v>0.85099999999999998</v>
+        <v>8.5099999999999998E-6</v>
       </c>
       <c r="F330">
         <v>157</v>
@@ -9000,19 +9012,19 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B331" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C331">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D331">
         <v>82864.5</v>
       </c>
       <c r="E331">
-        <v>2.3300000000000001E-2</v>
+        <v>2.3300000000000003E-7</v>
       </c>
       <c r="F331">
         <v>137</v>
@@ -9026,19 +9038,19 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B332" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C332">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D332">
         <v>100144</v>
       </c>
       <c r="E332">
-        <v>1.1299999999999999E-2</v>
+        <v>1.1300000000000001E-7</v>
       </c>
       <c r="F332">
         <v>118</v>
@@ -9052,19 +9064,19 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B333" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C333">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D333">
         <v>10460.5</v>
       </c>
       <c r="E333">
-        <v>0.35699999999999998</v>
+        <v>3.5700000000000001E-6</v>
       </c>
       <c r="F333">
         <v>108</v>
@@ -9078,19 +9090,19 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B334" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C334">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D334">
         <v>56381.4</v>
       </c>
       <c r="E334">
-        <v>1.17E-2</v>
+        <v>1.1700000000000002E-7</v>
       </c>
       <c r="F334">
         <v>88</v>
@@ -9104,19 +9116,19 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B335" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C335">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D335">
         <v>8094.2</v>
       </c>
       <c r="E335">
-        <v>7.22E-2</v>
+        <v>7.2200000000000003E-7</v>
       </c>
       <c r="F335">
         <v>78</v>
@@ -9130,19 +9142,19 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B336" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C336">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D336">
         <v>17123.400000000001</v>
       </c>
       <c r="E336">
-        <v>4.7199999999999999E-2</v>
+        <v>4.7200000000000004E-7</v>
       </c>
       <c r="F336">
         <v>69</v>
@@ -9156,19 +9168,19 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B337" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C337">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D337">
         <v>24807.9</v>
       </c>
       <c r="E337">
-        <v>1.52E-2</v>
+        <v>1.5200000000000001E-7</v>
       </c>
       <c r="F337">
         <v>61</v>
@@ -9182,19 +9194,19 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B338" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C338">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D338">
         <v>3260.3</v>
       </c>
       <c r="E338">
-        <v>0.36699999999999999</v>
+        <v>3.6700000000000004E-6</v>
       </c>
       <c r="F338">
         <v>53</v>
@@ -9208,19 +9220,19 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B339" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C339">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D339">
         <v>8275.6</v>
       </c>
       <c r="E339">
-        <v>8.6599999999999996E-2</v>
+        <v>8.6600000000000005E-7</v>
       </c>
       <c r="F339">
         <v>41</v>
@@ -9234,19 +9246,19 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B340" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C340">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D340">
         <v>20884.7</v>
       </c>
       <c r="E340">
-        <v>1.2200000000000001E-2</v>
+        <v>1.2200000000000001E-7</v>
       </c>
       <c r="F340">
         <v>33</v>
@@ -9260,19 +9272,19 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B341" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C341">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D341">
         <v>4824.7</v>
       </c>
       <c r="E341">
-        <v>0.124</v>
+        <v>1.2400000000000002E-6</v>
       </c>
       <c r="F341">
         <v>23</v>
@@ -9286,19 +9298,19 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B342" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C342">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D342">
         <v>6360.7</v>
       </c>
       <c r="E342">
-        <v>0.13500000000000001</v>
+        <v>1.3500000000000002E-6</v>
       </c>
       <c r="F342">
         <v>23</v>
@@ -9312,19 +9324,19 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B343" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C343">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D343">
         <v>14430.3</v>
       </c>
       <c r="E343">
-        <v>0.32800000000000001</v>
+        <v>3.2800000000000004E-6</v>
       </c>
       <c r="F343">
         <v>157</v>
@@ -9338,19 +9350,19 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B344" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C344">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D344">
         <v>11982.8</v>
       </c>
       <c r="E344">
-        <v>0.188</v>
+        <v>1.8800000000000002E-6</v>
       </c>
       <c r="F344">
         <v>137</v>
@@ -9364,19 +9376,19 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B345" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C345">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D345">
         <v>30471.8</v>
       </c>
       <c r="E345">
-        <v>0.04</v>
+        <v>4.0000000000000003E-7</v>
       </c>
       <c r="F345">
         <v>118</v>
@@ -9390,19 +9402,19 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B346" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C346">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D346">
         <v>7067.2</v>
       </c>
       <c r="E346">
-        <v>0.26300000000000001</v>
+        <v>2.6300000000000002E-6</v>
       </c>
       <c r="F346">
         <v>108</v>
@@ -9416,19 +9428,19 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B347" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C347">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D347">
         <v>64360.9</v>
       </c>
       <c r="E347">
-        <v>1.26E-2</v>
+        <v>1.2600000000000002E-7</v>
       </c>
       <c r="F347">
         <v>88</v>
@@ -9442,19 +9454,19 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B348" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C348">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D348">
         <v>3357</v>
       </c>
       <c r="E348">
-        <v>0.43099999999999999</v>
+        <v>4.3100000000000002E-6</v>
       </c>
       <c r="F348">
         <v>78</v>
@@ -9468,19 +9480,19 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B349" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C349">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D349">
         <v>12465.8</v>
       </c>
       <c r="E349">
-        <v>9.1899999999999996E-2</v>
+        <v>9.1900000000000001E-7</v>
       </c>
       <c r="F349">
         <v>69</v>
@@ -9494,19 +9506,19 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B350" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C350">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D350">
         <v>25493.599999999999</v>
       </c>
       <c r="E350">
-        <v>3.0099999999999998E-2</v>
+        <v>3.0100000000000001E-7</v>
       </c>
       <c r="F350">
         <v>61</v>
@@ -9520,19 +9532,19 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B351" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C351">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D351">
         <v>6195.6</v>
       </c>
       <c r="E351">
-        <v>0.32400000000000001</v>
+        <v>3.2400000000000003E-6</v>
       </c>
       <c r="F351">
         <v>53</v>
@@ -9546,19 +9558,19 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B352" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C352">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D352">
         <v>10842.3</v>
       </c>
       <c r="E352">
-        <v>0.11899999999999999</v>
+        <v>1.19E-6</v>
       </c>
       <c r="F352">
         <v>41</v>
@@ -9572,19 +9584,19 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B353" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C353">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D353">
         <v>33770.5</v>
       </c>
       <c r="E353">
-        <v>1.8800000000000001E-2</v>
+        <v>1.8800000000000002E-7</v>
       </c>
       <c r="F353">
         <v>33</v>
@@ -9598,19 +9610,19 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B354" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C354">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D354">
         <v>4669.8</v>
       </c>
       <c r="E354">
-        <v>0.753</v>
+        <v>7.5300000000000007E-6</v>
       </c>
       <c r="F354">
         <v>157</v>
@@ -9624,19 +9636,19 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B355" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C355">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D355">
         <v>15449</v>
       </c>
       <c r="E355">
-        <v>0.126</v>
+        <v>1.26E-6</v>
       </c>
       <c r="F355">
         <v>137</v>
@@ -9650,19 +9662,19 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B356" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C356">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D356">
         <v>94857</v>
       </c>
       <c r="E356">
-        <v>6.7600000000000004E-3</v>
+        <v>6.760000000000001E-8</v>
       </c>
       <c r="F356">
         <v>118</v>
@@ -9676,19 +9688,19 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B357" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C357">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D357">
         <v>14858.2</v>
       </c>
       <c r="E357">
-        <v>0.20200000000000001</v>
+        <v>2.0200000000000001E-6</v>
       </c>
       <c r="F357">
         <v>108</v>
@@ -9702,19 +9714,19 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B358" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C358">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D358">
         <v>80897.100000000006</v>
       </c>
       <c r="E358">
-        <v>9.3500000000000007E-3</v>
+        <v>9.350000000000001E-8</v>
       </c>
       <c r="F358">
         <v>88</v>
@@ -9728,19 +9740,19 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B359" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C359">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D359">
         <v>6509.9</v>
       </c>
       <c r="E359">
-        <v>0.40300000000000002</v>
+        <v>4.0300000000000004E-6</v>
       </c>
       <c r="F359">
         <v>78</v>
@@ -9754,19 +9766,19 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B360" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C360">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D360">
         <v>9724.2999999999993</v>
       </c>
       <c r="E360">
-        <v>0.108</v>
+        <v>1.08E-6</v>
       </c>
       <c r="F360">
         <v>69</v>
@@ -9780,19 +9792,19 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B361" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C361">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D361">
         <v>34593.199999999997</v>
       </c>
       <c r="E361">
-        <v>1.11E-2</v>
+        <v>1.1100000000000001E-7</v>
       </c>
       <c r="F361">
         <v>61</v>
@@ -9806,19 +9818,19 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B362" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C362">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D362">
         <v>5950</v>
       </c>
       <c r="E362">
-        <v>0.42499999999999999</v>
+        <v>4.25E-6</v>
       </c>
       <c r="F362">
         <v>53</v>
@@ -9832,19 +9844,19 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B363" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C363">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D363">
         <v>21711</v>
       </c>
       <c r="E363">
-        <v>2.0799999999999999E-2</v>
+        <v>2.0800000000000001E-7</v>
       </c>
       <c r="F363">
         <v>41</v>
@@ -9858,19 +9870,19 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B364" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C364">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D364">
         <v>18536.7</v>
       </c>
       <c r="E364">
-        <v>1.04E-2</v>
+        <v>1.04E-7</v>
       </c>
       <c r="F364">
         <v>33</v>
@@ -9884,19 +9896,19 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B365" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C365">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D365">
         <v>5148.3999999999996</v>
       </c>
       <c r="E365">
-        <v>3.1399999999999997E-2</v>
+        <v>3.1399999999999998E-7</v>
       </c>
       <c r="F365">
         <v>26</v>
@@ -9910,19 +9922,19 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B366" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C366">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D366">
         <v>11793.7</v>
       </c>
       <c r="E366">
-        <v>0.96399999999999997</v>
+        <v>9.6400000000000009E-6</v>
       </c>
       <c r="F366">
         <v>157</v>
@@ -9936,19 +9948,19 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B367" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C367">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D367">
         <v>73064.899999999994</v>
       </c>
       <c r="E367">
-        <v>3.2099999999999997E-2</v>
+        <v>3.2099999999999998E-7</v>
       </c>
       <c r="F367">
         <v>137</v>
@@ -9962,19 +9974,19 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B368" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C368">
-        <v>750</v>
+        <v>1023.15</v>
       </c>
       <c r="D368">
         <v>100101</v>
       </c>
       <c r="E368">
-        <v>1.23E-2</v>
+        <v>1.23E-7</v>
       </c>
       <c r="F368">
         <v>118</v>
@@ -9988,19 +10000,19 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B369" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C369">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D369">
         <v>22332.2</v>
       </c>
       <c r="E369">
-        <v>0.22700000000000001</v>
+        <v>2.2700000000000003E-6</v>
       </c>
       <c r="F369">
         <v>108</v>
@@ -10014,19 +10026,19 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B370" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C370">
-        <v>800</v>
+        <v>1073.1500000000001</v>
       </c>
       <c r="D370">
         <v>65778.2</v>
       </c>
       <c r="E370">
-        <v>2.8799999999999999E-2</v>
+        <v>2.8800000000000004E-7</v>
       </c>
       <c r="F370">
         <v>88</v>
@@ -10040,19 +10052,19 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B371" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C371">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D371">
         <v>10332.200000000001</v>
       </c>
       <c r="E371">
-        <v>0.443</v>
+        <v>4.4300000000000008E-6</v>
       </c>
       <c r="F371">
         <v>78</v>
@@ -10066,19 +10078,19 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B372" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C372">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D372">
         <v>13647.9</v>
       </c>
       <c r="E372">
-        <v>0.187</v>
+        <v>1.8700000000000001E-6</v>
       </c>
       <c r="F372">
         <v>69</v>
@@ -10092,19 +10104,19 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B373" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C373">
-        <v>850</v>
+        <v>1123.1500000000001</v>
       </c>
       <c r="D373">
         <v>23323</v>
       </c>
       <c r="E373">
-        <v>2.4400000000000002E-2</v>
+        <v>2.4400000000000001E-7</v>
       </c>
       <c r="F373">
         <v>61</v>
@@ -10118,19 +10130,19 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B374" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C374">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D374">
         <v>3313.3</v>
       </c>
       <c r="E374">
-        <v>0.22</v>
+        <v>2.2000000000000001E-6</v>
       </c>
       <c r="F374">
         <v>53</v>
@@ -10144,19 +10156,19 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B375" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C375">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D375">
         <v>10301.700000000001</v>
       </c>
       <c r="E375">
-        <v>3.5900000000000001E-2</v>
+        <v>3.5900000000000003E-7</v>
       </c>
       <c r="F375">
         <v>41</v>
@@ -10170,19 +10182,19 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B376" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C376">
-        <v>900</v>
+        <v>1173.1500000000001</v>
       </c>
       <c r="D376">
         <v>15862.1</v>
       </c>
       <c r="E376">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4500000000000007E-7</v>
       </c>
       <c r="F376">
         <v>33</v>
@@ -10196,19 +10208,19 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B377" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C377">
-        <v>950</v>
+        <v>1223.1500000000001</v>
       </c>
       <c r="D377">
         <v>6451.9</v>
       </c>
       <c r="E377">
-        <v>0.19900000000000001</v>
+        <v>1.9900000000000004E-6</v>
       </c>
       <c r="F377">
         <v>26</v>
